--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -2780,7 +2780,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132654052</v>
+        <v>132654053</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478202</v>
+        <v>478185</v>
       </c>
       <c r="R20" t="n">
-        <v>7019290</v>
+        <v>7019206</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2897,7 +2897,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132654053</v>
+        <v>132654052</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478185</v>
+        <v>478202</v>
       </c>
       <c r="R21" t="n">
-        <v>7019206</v>
+        <v>7019290</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3248,7 +3248,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132654050</v>
+        <v>132654048</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3279,7 +3279,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478258</v>
+        <v>478243</v>
       </c>
       <c r="R24" t="n">
-        <v>7019330</v>
+        <v>7019369</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,19 +3333,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack?</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3365,7 +3360,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132654048</v>
+        <v>132654050</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3396,7 +3391,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478243</v>
+        <v>478258</v>
       </c>
       <c r="R25" t="n">
-        <v>7019369</v>
+        <v>7019330</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,14 +3445,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack?</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>

--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -2419,32 +2419,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132654038</v>
+        <v>132654039</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478374</v>
+        <v>478372</v>
       </c>
       <c r="R17" t="n">
-        <v>7019502</v>
+        <v>7019472</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,32 +2541,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132654039</v>
+        <v>132654038</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478372</v>
+        <v>478374</v>
       </c>
       <c r="R18" t="n">
-        <v>7019472</v>
+        <v>7019502</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2780,7 +2780,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132654053</v>
+        <v>132654052</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478185</v>
+        <v>478202</v>
       </c>
       <c r="R20" t="n">
-        <v>7019206</v>
+        <v>7019290</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2897,7 +2897,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132654052</v>
+        <v>132654053</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478202</v>
+        <v>478185</v>
       </c>
       <c r="R21" t="n">
-        <v>7019290</v>
+        <v>7019206</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3248,7 +3248,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132654048</v>
+        <v>132654050</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3279,7 +3279,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478243</v>
+        <v>478258</v>
       </c>
       <c r="R24" t="n">
-        <v>7019369</v>
+        <v>7019330</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,14 +3333,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack?</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3360,7 +3365,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132654050</v>
+        <v>132654048</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3391,7 +3396,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478258</v>
+        <v>478243</v>
       </c>
       <c r="R25" t="n">
-        <v>7019330</v>
+        <v>7019369</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3445,19 +3450,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack?</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>

--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -2419,32 +2419,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132654039</v>
+        <v>132654038</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478372</v>
+        <v>478374</v>
       </c>
       <c r="R17" t="n">
-        <v>7019472</v>
+        <v>7019502</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,32 +2541,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132654038</v>
+        <v>132654039</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478374</v>
+        <v>478372</v>
       </c>
       <c r="R18" t="n">
-        <v>7019502</v>
+        <v>7019472</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -2780,7 +2780,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132654053</v>
+        <v>132654052</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478185</v>
+        <v>478202</v>
       </c>
       <c r="R20" t="n">
-        <v>7019206</v>
+        <v>7019290</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2897,7 +2897,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132654052</v>
+        <v>132654053</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478202</v>
+        <v>478185</v>
       </c>
       <c r="R21" t="n">
-        <v>7019290</v>
+        <v>7019206</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3248,7 +3248,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132654048</v>
+        <v>132654050</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3279,7 +3279,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478243</v>
+        <v>478258</v>
       </c>
       <c r="R24" t="n">
-        <v>7019369</v>
+        <v>7019330</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,14 +3333,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack?</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3360,7 +3365,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132654050</v>
+        <v>132654048</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3391,7 +3396,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478258</v>
+        <v>478243</v>
       </c>
       <c r="R25" t="n">
-        <v>7019330</v>
+        <v>7019369</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3445,19 +3450,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack?</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>

--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -2666,7 +2666,7 @@
         <v>132654062</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>132654052</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>132654053</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>132654058</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>132654057</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>132654050</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>132654048</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>132654047</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -2666,7 +2666,7 @@
         <v>132654062</v>
       </c>
       <c r="B19" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>132654052</v>
       </c>
       <c r="B20" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>132654053</v>
       </c>
       <c r="B21" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>132654058</v>
       </c>
       <c r="B22" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>132654057</v>
       </c>
       <c r="B23" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>132654050</v>
       </c>
       <c r="B24" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>132654048</v>
       </c>
       <c r="B25" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>132654047</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 18872-2026 artfynd.xlsx
+++ b/artfynd/A 18872-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>6744658</v>
       </c>
       <c r="B2" t="n">
-        <v>78471</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478314.3044767709</v>
+        <v>478314</v>
       </c>
       <c r="R2" t="n">
-        <v>7019452.686472042</v>
+        <v>7019453</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1993-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1993-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,53 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4706303</v>
+        <v>62326193</v>
       </c>
       <c r="B3" t="n">
-        <v>97039</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222356</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Frösöstarr</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pediformis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C. A. Mey.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vid Tängsågen, Sågbäcken, Ås, Jmt</t>
+          <t>Tängskogen, Sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478314.3044767709</v>
+        <v>478275</v>
       </c>
       <c r="R3" t="n">
-        <v>7019452.686472042</v>
+        <v>7019359</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,27 +848,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1993-07-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1993-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Några ex. Tängskogen; Sågbäcken; södra delen, västra sidan, ca 400 m söder om kraftledningen, intill stigen,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,39 +870,38 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, örtrik bäckdråg,</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anita Andersson, Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>104469071</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -960,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478382.938340673</v>
+        <v>478382</v>
       </c>
       <c r="R4" t="n">
-        <v>7019480.55480073</v>
+        <v>7019481</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,19 +963,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104478318</v>
+        <v>132654038</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,37 +1003,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Patronbodarna, Jmt</t>
+          <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478365.2321059862</v>
+        <v>478374</v>
       </c>
       <c r="R5" t="n">
-        <v>7019459.088725125</v>
+        <v>7019502</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1057,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,31 +1083,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104478316</v>
+        <v>132654040</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,37 +1125,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Patronbodarna, Jmt</t>
+          <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478352.4818241288</v>
+        <v>478346</v>
       </c>
       <c r="R6" t="n">
-        <v>7019438.038919413</v>
+        <v>7019485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,22 +1179,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,70 +1205,79 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62326193</v>
+        <v>132654045</v>
       </c>
       <c r="B7" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tängskogen, Sågbäcken, Jmt</t>
+          <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478275.3951152874</v>
+        <v>478345</v>
       </c>
       <c r="R7" t="n">
-        <v>7019358.961758764</v>
+        <v>7019340</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,27 +1301,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1994-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1994-12-31</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Några ex. Tängskogen; Sågbäcken; södra delen, västra sidan, ca 400 m söder om kraftledningen, intill stigen,</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,38 +1328,44 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, örtrik bäckdråg,</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anita Andersson, Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132654061</v>
+        <v>132654046</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1418,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478293</v>
+        <v>478329</v>
       </c>
       <c r="R8" t="n">
-        <v>7019194</v>
+        <v>7019327</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1453,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,6 +1449,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1490,14 +1480,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132654045</v>
+        <v>132654049</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1525,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478345</v>
+        <v>478233</v>
       </c>
       <c r="R9" t="n">
-        <v>7019340</v>
+        <v>7019329</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1560,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,21 +1571,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1612,14 +1587,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132654046</v>
+        <v>132654056</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1647,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478329</v>
+        <v>478201</v>
       </c>
       <c r="R10" t="n">
-        <v>7019327</v>
+        <v>7019200</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1682,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,21 +1678,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1734,14 +1694,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132654040</v>
+        <v>132654060</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1769,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478346</v>
+        <v>478270</v>
       </c>
       <c r="R11" t="n">
-        <v>7019485</v>
+        <v>7019166</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1804,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,21 +1785,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1856,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132654055</v>
+        <v>132654061</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478170</v>
+        <v>478293</v>
       </c>
       <c r="R12" t="n">
-        <v>7019188</v>
+        <v>7019194</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1926,7 +1871,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1881,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132654051</v>
+        <v>104468590</v>
       </c>
       <c r="B13" t="n">
-        <v>58119</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,45 +1919,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>sågbäcken, Jmt</t>
+          <t>Patronbodarna Ö , Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478283</v>
+        <v>478414</v>
       </c>
       <c r="R13" t="n">
-        <v>7019325</v>
+        <v>7019533</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,27 +1974,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Merlin</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,22 +1994,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132654056</v>
+        <v>132654042</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2118,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478201</v>
+        <v>478342</v>
       </c>
       <c r="R14" t="n">
-        <v>7019200</v>
+        <v>7019483</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2153,7 +2076,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2086,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,6 +2097,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2190,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132654060</v>
+        <v>132654047</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,34 +2139,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478270</v>
+        <v>478249</v>
       </c>
       <c r="R15" t="n">
-        <v>7019166</v>
+        <v>7019378</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2260,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2217,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på minst 2 granar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132654042</v>
+        <v>132654048</v>
       </c>
       <c r="B16" t="n">
-        <v>80438</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,34 +2260,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478342</v>
+        <v>478243</v>
       </c>
       <c r="R16" t="n">
-        <v>7019483</v>
+        <v>7019369</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2367,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2334,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,21 +2345,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2419,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132654038</v>
+        <v>132654050</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,37 +2372,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478374</v>
+        <v>478258</v>
       </c>
       <c r="R17" t="n">
-        <v>7019502</v>
+        <v>7019330</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,32 +2446,22 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack?</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2541,48 +2478,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132654039</v>
+        <v>132654052</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478372</v>
+        <v>478202</v>
       </c>
       <c r="R18" t="n">
-        <v>7019472</v>
+        <v>7019290</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2611,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2621,7 +2563,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,21 +2579,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2663,7 +2595,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132654062</v>
+        <v>132654053</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2703,13 +2635,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478305</v>
+        <v>478185</v>
       </c>
       <c r="R19" t="n">
-        <v>7019208</v>
+        <v>7019206</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2738,7 +2670,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2680,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2780,7 +2712,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132654052</v>
+        <v>132654057</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2820,7 +2752,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478202</v>
+        <v>478270</v>
       </c>
       <c r="R20" t="n">
         <v>7019290</v>
@@ -2855,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2797,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2897,7 +2829,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132654053</v>
+        <v>132654058</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2928,7 +2860,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2937,13 +2869,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478185</v>
+        <v>478279</v>
       </c>
       <c r="R21" t="n">
-        <v>7019206</v>
+        <v>7019283</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2972,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,19 +2914,19 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack?</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -3014,7 +2946,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132654058</v>
+        <v>132654062</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -3045,7 +2977,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3054,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478279</v>
+        <v>478305</v>
       </c>
       <c r="R22" t="n">
-        <v>7019283</v>
+        <v>7019208</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3089,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,19 +3031,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack?</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3131,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132654057</v>
+        <v>132654051</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,42 +3074,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478270</v>
+        <v>478283</v>
       </c>
       <c r="R23" t="n">
-        <v>7019290</v>
+        <v>7019325</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3206,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,12 +3151,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Merlin</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3248,53 +3183,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132654050</v>
+        <v>104468682</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>sågbäcken, Jmt</t>
+          <t>Patronbodarna Ö , Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478258</v>
+        <v>478411</v>
       </c>
       <c r="R24" t="n">
-        <v>7019330</v>
+        <v>7019502</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3318,34 +3249,19 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack?</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3353,65 +3269,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132654048</v>
+        <v>104478315</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>sågbäcken, Jmt</t>
+          <t>Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478243</v>
+        <v>478366</v>
       </c>
       <c r="R25" t="n">
-        <v>7019369</v>
+        <v>7019370</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3435,22 +3346,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,69 +3366,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132654047</v>
+        <v>104478316</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>sågbäcken, Jmt</t>
+          <t>Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478249</v>
+        <v>478352</v>
       </c>
       <c r="R26" t="n">
-        <v>7019378</v>
+        <v>7019438</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3551,27 +3443,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringhack på minst 2 granar</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3586,15 +3463,545 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104478318</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Patronbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>478365</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7019459</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104478319</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Patronbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>478384</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7019531</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132654039</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>sågbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>478372</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7019472</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Mattias Dalkvist</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Mattias Dalkvist</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132654055</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>sågbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>478170</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7019188</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4706303</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99869</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222356</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Frösöstarr</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carex pediformis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>C. A. Mey.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vid Tängsågen, Sågbäcken, Ås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>478314</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7019453</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>1993-07-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1993-07-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
